--- a/data_extactor/batch_10_fa/batch_0048_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0048_fa.xlsx
@@ -493,12 +493,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Naturopathic Physicians (پزشکان ناتوروپاتی)</t>
+          <t>پزشکان ناتوروپاتی (Naturopathic Physicians)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Doctor (Dr) | Naturopathic Doctor | Naturopathic Endocrinologist | Naturopathic Medicine Doctor | Naturopathic Oncologist | Naturopathic Oncology Provider | Physician</t>
+          <t>پزشک (Dr) | پزشک طب طبیعی | متخصص غدد طب طبیعی | پزشک طب طبیعی | متخصص سرطان طب طبیعی | ارائه‌دهنده خدمات سرطان‌شناسی طب طبیعی | پزشک</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | سخنوری | تفکر انتقادی | نوشتن | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | زبان انگلیسی | شیمی | آموزش و پرورش | فروش و بازاریابی | اداری | مدیریت و اداره | جامعه‌شناسی و مردم‌شناسی | اقتصاد و حسابداری | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | زبان انگلیسی | شیمی | آموزش و پرورش | فروش و بازاریابی | اداری | مدیریت و اداره | جامعه‌شناسی و انسان‌شناسی | اقتصاد و حسابداری | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک نوشتاری | تشخیص گفتار | وضوح گفتار | نظم‌دهی اطلاعات | دید نزدیک | بیان نوشتاری | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستار | اصالت | توجه انتخابی | دید دور | سرعت ادراکی</t>
+          <t>حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان کتبی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستار | اصالت | توجه انتخابی | بینایی دور | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | تناوب تصمیم‌گیری | اهمیت دقت یا صحت | در معرض بیماری یا عفونت بودن | محیط داخلی و کنترل‌شده از نظر محیطی | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نزدیکی فیزیکی | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | صرف زمان برای نشستن | پیامد خطا</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نزدیکی فیزیکی | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | صرف زمان برای نشستن | پیامد خطا</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Acupuncturists | Advanced Practice Psychiatric Nurses | Allergists and Immunologists | Cardiologists | Chiropractors | Dermatologists | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Neurologists | Nurse Practitioners | Obstetricians and Gynecologists | Ophthalmologists, Except Pediatric | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Physician Assistants | Psychiatrists | Urologists</t>
+          <t>طب‌سوزنی‌ها | پرستاران پیشرفته روانپزشکی | متخصصان آلرژی و ایمونولوژی | متخصصان قلب | کایروپراکتورها | متخصصان پوست | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Orthoptists (ارتوپتیست‌ها)</t>
+          <t>ارتوپتیست‌ها (Orthoptists)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Certified Orthoptist | Clinical Orthoptist (CO) | Orthoptist</t>
+          <t>ارتوپتیست دارای گواهی صلاحیت | ارتوپتیست بالینی (CO) | ارتوپتیست</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | سخنوری | درک مطلب | علوم | نوشتن | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | علوم | نگارش | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | پزشکی و دندانپزشکی | خدمات مشتری و شخصی | آموزش و پرورش | روان‌شناسی | زیست‌شناسی</t>
+          <t>زبان انگلیسی | پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | آموزش و پرورش | روان‌شناسی | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | دید نزدیک | روانی ایده‌ها | سرعت ادراکی | انعطاف‌پذیری بستار | نظم‌دهی اطلاعات | اصالت | تشخیص رنگ بصری | دید دور | مهارت انگشتان | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | روانی ایده‌ها | سرعت ادراکی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | اصالت | تشخیص رنگ بصری | بینایی دور | مهارت انگشتان | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی و کنترل‌شده از نظر محیطی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقت یا صحت | ایمیل | مکالمات تلفنی | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نزدیکی فیزیکی | در معرض بیماری یا عفونت بودن | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تناوب تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | فشار زمانی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | ایمیل | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نزدیکی فیزیکی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | فشار زمانی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Allergists and Immunologists | Anesthesiologists | Clinical Nurse Specialists | Dermatologists | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Neurologists | Nurse Practitioners | Obstetricians and Gynecologists | Ophthalmic Medical Technologists | Ophthalmologists, Except Pediatric | Optometrists | Pediatric Surgeons | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Physician Assistants | Physicians, Pathologists | Psychiatrists | Respiratory Therapists</t>
+          <t>متخصصان آلرژی و ایمونولوژی | متخصصان بیهوشی | متخصصان پرستاری بالینی | متخصصان پوست | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | تکنولوژیست‌های پزشکی چشم‌پزشکی | چشم‌پزشکان، به‌جز کودکان | اپتومتریست‌ها | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | پزشکان، آسیب‌شناسان | روان‌پزشکان | درمانگران تنفسی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,42 +607,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Medical and Clinical Laboratory Technologists (تکنولوژیست‌های آزمایشگاه پزشکی و بالینی)</t>
+          <t>تکنولوژیست‌های آزمایشگاه پزشکی و بالینی (Medical and Clinical Laboratory Technologists)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Clinical Chemist | Clinical Laboratory Scientist (CLS) | Clinical Laboratory Technologist | Histologist Technologist | Lab Tech (Laboratory Technologist) | MLS (Medical Laboratory Scientist) | Medical Lab Technologist (Medical Laboratory Technologist) | Medical Technologist (MT) | Microbiology Technologist (MT) | Technologist</t>
+          <t>شیمی‌دان بالینی | دانشمند آزمایشگاه بالینی (CLS) | تکنولوژیست آزمایشگاه بالینی | تکنولوژیست بافت‌شناسی | تکنولوژیست آزمایشگاه (Lab Tech) | MLS (دانشمند آزمایشگاه پزشکی) | تکنولوژیست آزمایشگاه پزشکی (Medical Lab Technologist) | تکنولوژیست پزشکی (MT) | تکنولوژیست میکروب‌شناسی (MT) | تکنولوژیست</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار صفحه‌خوان تجاری Commercial plate reader software | نرم‌افزار پایگاه داده | نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار ایمیل | FileMaker Pro | نرم‌افزار مدیریت گردش کار آزمایشگاه هماتولوژی | سیستم اطلاعات آزمایشگاهی LIS | نرم‌افزار MEDITECH | نرم‌افزار تصویربرداری دیجیتال پزشکی | نرم‌افزار کدگذاری روش‌های پزشکی | نرم‌افزار یکپارچه‌سازی سیستم‌های پزشکی | نرم‌افزار ثبت تصویر میکروسکوپی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Word | نرم‌افزار کنترل کیفیت | نرم‌افزار غربالگری بازپرداخت | نرم‌افزار ردیابی نمونه | نرم‌افزار تحویل نتایج تست | نرم‌افزار مسیریابی تست | نرم‌افزار EHR eClinicalWorks</t>
+          <t>نرم‌افزار صفحه‌خوان تجاری Commercial plate reader software | نرم‌افزار پایگاه داده | نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار ایمیل | FileMaker Pro | نرم‌افزار مدیریت گردش کار آزمایشگاه هماتولوژی | سیستم اطلاعات آزمایشگاهی LIS | نرم‌افزار MEDITECH | نرم‌افزار تصویربرداری دیجیتال پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | نرم‌افزار یکپارچه‌سازی سیستم‌های پزشکی | نرم‌افزار ثبت تصویر میکروسکوپی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Word | نرم‌افزار کنترل کیفیت | نرم‌افزار غربالگری بازپرداخت | نرم‌افزار ردیابی نمونه | نرم‌افزار تحویل نتایج تست | نرم‌افزار مسیریابی تست | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | علوم | گوش دادن فعال | درک مطلب | نظارت | یادگیری فعال | نوشتن | سخنوری | ریاضیات</t>
+          <t>تفکر انتقادی | علوم | گوش دادن فعال | درک مطلب | نظارت | یادگیری فعال | نگارش | سخن گفتن | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>شیمی | خدمات مشتری و شخصی | کامپیوتر و الکترونیک | زبان انگلیسی | زیست‌شناسی | ریاضیات | اداری | پزشکی و دندانپزشکی | آموزش و پرورش | مکانیکی</t>
+          <t>شیمی | خدمات مشتری و شخصی | رایانه و الکترونیک | زبان انگلیسی | زیست‌شناسی | ریاضیات | اداری | پزشکی و دندان‌پزشکی | آموزش و پرورش | مکانیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دید نزدیک | استدلال استقرایی | درک نوشتاری | حساسیت به مسئله | نظم‌دهی اطلاعات | درک شفاهی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | ثبات دست و بازو | دقت کنترل | مهارت انگشتان | انعطاف‌پذیری بستار | توجه انتخابی | تشخیص گفتار | تشخیص رنگ بصری | بیان نوشتاری | مهارت دستی | سرعت ادراکی | سرعت بستار | استدلال ریاضی | وضوح گفتار | دید دور | تجسم | تسهیل اعداد</t>
+          <t>بینایی نزدیک | استدلال استقرایی | درک کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک شفاهی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | ثبات دست و بازو | دقت کنترل | مهارت انگشتان | انعطاف‌پذیری بستار | توجه انتخابی | تشخیص گفتار | تشخیص رنگ بصری | بیان کتبی | مهارت دستی | سرعت ادراکی | سرعت بستار | استدلال ریاضی | وضوح گفتار | بینایی دور | تجسم | توانایی عددی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | اهمیت دقت یا صحت | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ایمیل | محیط داخلی و کنترل‌شده از نظر محیطی | در معرض بیماری یا عفونت بودن | بحث‌های حضوری با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تناوب تصمیم‌گیری | اهمیت تکرار وظایف یکسان | فشار زمانی | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا | نزدیکی فیزیکی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تعامل با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان</t>
+          <t>مکالمات تلفنی | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | فشار زمانی | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعامل با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Biological Technicians | Cardiologists | Cardiovascular Technologists and Technicians | Chemical Technicians | Chemists | Cytogenetic Technologists | Cytotechnologists | Diagnostic Medical Sonographers | Histology Technicians | Histotechnologists | Medical Scientists, Except Epidemiologists | Medical and Clinical Laboratory Technicians | Microbiologists | Neurodiagnostic Technologists | Nuclear Medicine Technologists | Phlebotomists | Physicians, Pathologists | Radiologic Technologists and Technicians | Radiologists | Surgical Technologists</t>
+          <t>تکنسین‌های زیستی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | تکنسین‌های شیمی | شیمی‌دانان | تکنولوژیست‌های سیتوژنتیک | سیتوتکنولوژیست‌ها | سونوگرافیست‌های پزشکی تشخیصی | تکنیسین‌های هیستولوژی | هیستوتکنولوژیست‌ها | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | تکنیسین‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی هسته‌ای | فلبوتومیست‌ها | پزشکان، آسیب‌شناسان | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,42 +664,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cytogenetic Technologists (تکنولوژیست‌های سیتوژنتیک)</t>
+          <t>تکنولوژیست‌های سیتوژنتیک (Cytogenetic Technologists)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Certified Cytogenetic Technologist | Clinical Cytogeneticist Scientist (CCS) | Cytogenetic Technologist | Cytogenetics Clinical Laboratory Specialist (CG CLSp) | Cytogenetics Technical Specialist | Cytogenetics Technologist | Molecular Genetics Technologist</t>
+          <t>تکنولوژیست سیتوژنتیک دارای گواهی صلاحیت | دانشمند سیتوژنتیک بالینی (CCS) | تکنولوژیست سیتوژنتیک | کارشناس آزمایشگاه بالینی سیتوژنتیک (CG CLSp) | کارشناس فنی سیتوژنتیک | تکنولوژیست سیتوژنتیک | تکنولوژیست ژنتیک مولکولی</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Adobe Illustrator | C++ | نرم‌افزار ثبت تصویر خودکار Cell Bioscience | نرم‌افزار کاریوتایپینگ دیجیتال | Genetix CytoVision | Genial Genetics Shire | سیستم مدیریت کیفیت Genial Genetics iPassport QMS | Geniel Genetics iGene | نرم‌افزار تجزیه و تحلیل تصویر | نرم‌افزار ثبت تصویر | KARIO | LUCIA MFISH | Lucia CGH | Lucia Comet Assay | Lucia FISH | Lucia Karyo | Lucia Metaphase Finder | MetaSystems Isis Color Karyotyping | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Python</t>
+          <t>Adobe Illustrator | C++ | نرم‌افزار ثبت تصویر خودکار Cell Bioscience | نرم‌افزار کاریوتایپینگ دیجیتال | Genetix CytoVision | Genial Genetics Shire | سیستم مدیریت کیفیت Genial Genetics iPassport QMS | Geniel Genetics iGene | نرم‌افزار تحلیل تصویر | نرم‌افزار ثبت تصویر | KARIO | LUCIA MFISH | Lucia CGH | Lucia Comet Assay | Lucia FISH | Lucia Karyo | Lucia Metaphase Finder | MetaSystems Isis Color Karyotyping | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Python</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نوشتن | سخنوری | گوش دادن فعال | یادگیری فعال | علوم | نظارت | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | نگارش | سخن گفتن | گوش دادن فعال | یادگیری فعال | علوم | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | شیمی | زبان انگلیسی | کامپیوتر و الکترونیک | ریاضیات</t>
+          <t>زیست‌شناسی | شیمی | زبان انگلیسی | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | نظم‌دهی اطلاعات | دید نزدیک | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بیان نوشتاری | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | سرعت ادراکی | تسهیل اعداد | استدلال ریاضی | روانی ایده‌ها | مهارت انگشتان | ثبات دست و بازو</t>
+          <t>درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | سرعت ادراکی | توانایی عددی | استدلال ریاضی | روانی ایده‌ها | مهارت انگشتان | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>محیط داخلی و کنترل‌شده از نظر محیطی | اهمیت دقت یا صحت | بحث‌های حضوری با افراد و درون تیم‌ها | فشار زمانی | تناوب تصمیم‌گیری | اهمیت تکرار وظایف یکسان | ایمیل | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای انجام حرکات تکراری | پیامد خطا | در معرض شرایط خطرناک بودن | صرف زمان برای نشستن | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | در معرض بیماری یا عفونت بودن | مکالمات تلفنی | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | ایمیل | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای انجام حرکات تکراری | پیامد خطا | قرار گرفتن در معرض شرایط خطرناک | صرف زمان برای نشستن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | مکالمات تلفنی | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Biochemists and Biophysicists | Bioengineers and Biomedical Engineers | Bioinformatics Scientists | Biological Technicians | Cardiovascular Technologists and Technicians | Cytotechnologists | Geneticists | Histology Technicians | Histotechnologists | Medical Scientists, Except Epidemiologists | Medical and Clinical Laboratory Technicians | Medical and Clinical Laboratory Technologists | Microbiologists | Molecular and Cellular Biologists | Neurodiagnostic Technologists | Nuclear Medicine Technologists | Phlebotomists | Physicians, Pathologists | Radiologic Technologists and Technicians | Radiologists</t>
+          <t>بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های زیستی | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | سیتوتکنولوژیست‌ها | ژنتیک‌دان‌ها | تکنیسین‌های هیستولوژی | هیستوتکنولوژیست‌ها | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان مولکولی و سلولی | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی هسته‌ای | فلبوتومیست‌ها | پزشکان، آسیب‌شناسان | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,42 +721,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cytotechnologists (سیتوتکنولوژیست‌ها)</t>
+          <t>سیتوتکنولوژیست‌ها (Cytotechnologists)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cytologist | Cytology Applications Specialist | Cytology Coordinator | Cytology Technical Specialist | Cytotechnologist</t>
+          <t>سیتولوژیست (یاخته‌شناس) | کارشناس کاربردهای سیتولوژی | هماهنگ‌کننده سیتولوژی | کارشناس فنی سیتولوژی | سیتوتکنولوژیست</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار Ansible | Antek HealthWare LabDAQ | Aspyra CyberLAB | سیستم CPSI CPSI System | CSS CLS-2000 | Cerner Millennium PathNet | ClinLab LIS | Clinical Software Solutions CLIN1 Suite | Comp Pro Med Polytech | Custom Software Systems StarLab | Elekta Impac Software IntelliLab | EpicLab Laboratory Information System | Fletcher-Flora Health Care Systems FFlex eSuite LIS | Fletcher-Flora Health Care Systems LabPak LIS | Fortius Lab Systems Clinical LIS | GE Healthcare Centricity Laboratory | HEX Laboratory Systems LAB/HEX | Healthvision TDSynergy LIS | LabSoft LabNet | سیستم اطلاعات آزمایشگاهی LIS | نرم‌افزار MEDITECH | McKesson Horizon Lab | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | Multidata Computer Systems MultiTech | NeTLIMS AutoLIMS Core Lab | Omnitech OMNILAB | Orchard Software Orchard Harvest LIS | Prognosis Innovation Healthcare ChartAccess | Psyche Systems LabWeb | Quality Software Systems LabHealth | SCC Soft Computer SoftLab | STARLIMS | Schuyler House SchuyLab | Seacoast Laboratory Data Systems SurroundLab Plus | Siemens NOVIUS Lab | Sunquest Information Systems Sunquest Laboratory | eTeleNext LIS</t>
+          <t>نرم‌افزار Ansible | Antek HealthWare LabDAQ | Aspyra CyberLAB | CPSI CPSI System | CSS CLS-2000 | Cerner Millennium PathNet | ClinLab LIS | Clinical Software Solutions CLIN1 Suite | Comp Pro Med Polytech | Custom Software Systems StarLab | Elekta Impac Software IntelliLab | EpicLab Laboratory Information System | Fletcher-Flora Health Care Systems FFlex eSuite LIS | Fletcher-Flora Health Care Systems LabPak LIS | Fortius Lab Systems Clinical LIS | GE Healthcare Centricity Laboratory | HEX Laboratory Systems LAB/HEX | Healthvision TDSynergy LIS | LabSoft LabNet | سیستم اطلاعات آزمایشگاهی LIS | نرم‌افزار MEDITECH | McKesson Horizon Lab | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | Multidata Computer Systems MultiTech | NeTLIMS AutoLIMS Core Lab | Omnitech OMNILAB | Orchard Software Orchard Harvest LIS | Prognosis Innovation Healthcare ChartAccess | Psyche Systems LabWeb | Quality Software Systems LabHealth | SCC Soft Computer SoftLab | STARLIMS | Schuyler House SchuyLab | Seacoast Laboratory Data Systems SurroundLab Plus | Siemens NOVIUS Lab | Sunquest Information Systems Sunquest Laboratory | eTeleNext LIS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخنوری | نظارت | یادگیری فعال | نوشتن</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | پزشکی و دندانپزشکی | زبان انگلیسی | اداری</t>
+          <t>زیست‌شناسی | پزشکی و دندان‌پزشکی | زبان انگلیسی | اداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | دید نزدیک | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری بستار | ثبات دست و بازو | مهارت انگشتان | تشخیص رنگ بصری | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | توجه انتخابی | وضوح گفتار | تشخیص گفتار | دید دور | دقت کنترل | مهارت دستی | بیان نوشتاری</t>
+          <t>درک شفاهی | درک کتبی | بینایی نزدیک | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری بستار | ثبات دست و بازو | مهارت انگشتان | تشخیص رنگ بصری | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | توجه انتخابی | وضوح گفتار | تشخیص گفتار | بینایی دور | دقت کنترل | مهارت دستی | بیان کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>محیط داخلی و کنترل‌شده از نظر محیطی | اهمیت دقت یا صحت | صرف زمان برای انجام حرکات تکراری | ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در معرض بیماری یا عفونت بودن | تناوب تصمیم‌گیری | فشار زمانی | در معرض شرایط خطرناک بودن | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | فراوانی تصمیم‌گیری | فشار زمانی | قرار گرفتن در معرض شرایط خطرناک | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cardiovascular Technologists and Technicians | Cytogenetic Technologists | Endoscopy Technicians | Histology Technicians | Histotechnologists | Medical Equipment Preparers | Medical Scientists, Except Epidemiologists | Medical and Clinical Laboratory Technicians | Medical and Clinical Laboratory Technologists | Microbiologists | Neurodiagnostic Technologists | Nuclear Medicine Technologists | Ophthalmic Medical Technicians | Ophthalmic Medical Technologists | Phlebotomists | Physicians, Pathologists | Radiologic Technologists and Technicians | Radiologists | Surgical Assistants | Surgical Technologists</t>
+          <t>تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | تکنولوژیست‌های سیتوژنتیک | تکنسین‌های آندوسکوپی | تکنیسین‌های هیستولوژی | هیستوتکنولوژیست‌ها | آماده‌سازان تجهیزات پزشکی | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی هسته‌ای | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | فلبوتومیست‌ها | پزشکان، آسیب‌شناسان | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Histotechnologists (هیستوتکنولوژیست‌ها)</t>
+          <t>هیستوتکنولوژیست‌ها (Histotechnologists)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Clinical Lab Manager (Clinical Laboratory Manager) | Histology Lab Manager (Histology Laboratory Manager) | Histology Specialist | Histology Technologist | Histotechnologist</t>
+          <t>مدیر آزمایشگاه بالینی (Clinical Lab Manager) | مدیر آزمایشگاه بافت‌شناسی (Histology Lab Manager) | کارشناس بافت‌شناسی | تکنولوژیست بافت‌شناسی | تکنولوژیست بافت‌شناسی</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | سخنوری | گوش دادن فعال | یادگیری فعال | نوشتن | علوم</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | یادگیری فعال | نگارش | علوم</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | تولید و پردازش | شیمی | خدمات مشتری و شخصی | زبان انگلیسی | اداری | آموزش و پرورش</t>
+          <t>زیست‌شناسی | تولید و فرآوری | شیمی | خدمات مشتری و شخصی | زبان انگلیسی | اداری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک نوشتاری | ثبات دست و بازو | درک شفاهی | حساسیت به مسئله | بیان نوشتاری | بیان شفاهی | استدلال قیاسی | نظم‌دهی اطلاعات | توجه انتخابی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | دید دور | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | دقت کنترل | انعطاف‌پذیری بستار</t>
+          <t>بینایی نزدیک | درک کتبی | ثبات دست و بازو | درک شفاهی | حساسیت به مسئله | بیان کتبی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | توجه انتخابی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | بینایی دور | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | دقت کنترل | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>محیط داخلی و کنترل‌شده از نظر محیطی | فشار زمانی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | در معرض شرایط خطرناک بودن | ایمیل | اهمیت دقت یا صحت | اهمیت تکرار وظایف یکسان | بحث‌های حضوری با افراد و درون تیم‌ها | در معرض آلاینده‌ها بودن | مکالمات تلفنی | پیامد خطا | کار با یا مشارکت در یک گروه کاری یا تیم | تناوب تصمیم‌گیری | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | در معرض بیماری یا عفونت بودن | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض شرایط خطرناک | ایمیل | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | مکالمات تلفنی | پیامد خطا | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Biological Technicians | Cardiovascular Technologists and Technicians | Chemical Technicians | Cytogenetic Technologists | Cytotechnologists | Endoscopy Technicians | Histology Technicians | Medical Equipment Preparers | Medical and Clinical Laboratory Technicians | Medical and Clinical Laboratory Technologists | Microbiologists | Neurodiagnostic Technologists | Nuclear Medicine Technologists | Ophthalmic Medical Technologists | Phlebotomists | Physicians, Pathologists | Radiologic Technologists and Technicians | Surgical Assistants | Surgical Technologists | Veterinary Technologists and Technicians</t>
+          <t>تکنسین‌های زیستی | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | تکنسین‌های شیمی | تکنولوژیست‌های سیتوژنتیک | سیتوتکنولوژیست‌ها | تکنسین‌های آندوسکوپی | تکنیسین‌های هیستولوژی | آماده‌سازان تجهیزات پزشکی | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی هسته‌ای | تکنولوژیست‌های پزشکی چشم‌پزشکی | فلبوتومیست‌ها | پزشکان، آسیب‌شناسان | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | دستیاران جراحی | تکنولوژیست‌های جراحی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,42 +835,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Medical and Clinical Laboratory Technicians (تکنیسین‌های آزمایشگاه پزشکی و بالینی)</t>
+          <t>تکنیسین‌های آزمایشگاه پزشکی و بالینی (Medical and Clinical Laboratory Technicians)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Certified Clinical Laboratory Technician | Clinical Laboratory Technician (Clinical Lab Technician) | Laboratory Assistant (Lab Assistant) | Laboratory Technician (Lab Tech) | Medical Laboratory Technician (MLT) | Medical Laboratory Technicians (Medical Lab Technician) | Medical Technician</t>
+          <t>تکنسین آزمایشگاه بالینی دارای گواهی صلاحیت | تکنسین آزمایشگاه بالینی (Clinical Lab Technician) | دستیار آزمایشگاه | تکنسین آزمایشگاه | تکنسین آزمایشگاه پزشکی (MLT) | تکنسین آزمایشگاه پزشکی (Medical Lab Technician) | تکنسین پزشکی</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>نرم‌افزار صورت‌حساب | نرم‌افزار صفحه‌خوان تجاری Commercial plate reader software | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار ایمیل | FileMaker Pro | Google Docs | نرم‌افزار مدیریت گردش کار آزمایشگاه هماتولوژی | IBM Notes | سیستم اطلاعات آزمایشگاهی LIS | نرم‌افزار MEDITECH | نرم‌افزار تصویربرداری دیجیتال پزشکی | نرم‌افزار یکپارچه‌سازی سیستم‌های پزشکی | نرم‌افزار ثبت تصویر میکروسکوپی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Minitab | National Instruments LabVIEW | نرم‌افزار کنترل کیفیت | Quizlet | نرم‌افزار غربالگری بازپرداخت | نرم‌افزار SAP | نرم‌افزار ردیابی نمونه | Sunquest Information Systems Sunquest Laboratory | نرم‌افزار تحویل نتایج تست | نرم‌افزار مسیریابی تست</t>
+          <t>نرم‌افزار صدور صورتحساب | نرم‌افزار صفحه‌خوان تجاری Commercial plate reader software | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار ایمیل | FileMaker Pro | Google Docs | نرم‌افزار مدیریت گردش کار آزمایشگاه هماتولوژی | IBM Notes | سیستم اطلاعات آزمایشگاهی LIS | نرم‌افزار MEDITECH | نرم‌افزار تصویربرداری دیجیتال پزشکی | نرم‌افزار یکپارچه‌سازی سیستم‌های پزشکی | نرم‌افزار ثبت تصویر میکروسکوپی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Minitab | National Instruments LabVIEW | نرم‌افزار کنترل کیفیت | Quizlet | نرم‌افزار غربالگری بازپرداخت | نرم‌افزار SAP | نرم‌افزار ردیابی نمونه | Sunquest Information Systems Sunquest Laboratory | نرم‌افزار تحویل نتایج تست | نرم‌افزار مسیریابی تست</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | سخنوری | تفکر انتقادی | علوم | نظارت | نوشتن | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | علوم | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>شیمی | زیست‌شناسی | زبان انگلیسی | ریاضیات | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | اداری | پزشکی و دندانپزشکی</t>
+          <t>شیمی | زیست‌شناسی | زبان انگلیسی | ریاضیات | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | اداری | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | نظم‌دهی اطلاعات | بیان شفاهی | درک شفاهی | مهارت انگشتان | درک نوشتاری | استدلال قیاسی | بیان نوشتاری | مهارت دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | دقت کنترل | استدلال ریاضی | استدلال استقرایی | سرعت ادراکی | تسهیل اعداد</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | مهارت انگشتان | درک کتبی | استدلال قیاسی | بیان کتبی | مهارت دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | دقت کنترل | استدلال ریاضی | استدلال استقرایی | سرعت ادراکی | توانایی عددی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی و کنترل‌شده از نظر محیطی | اهمیت دقت یا صحت | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | در معرض بیماری یا عفونت بودن | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | فشار زمانی | پیامد خطا | در معرض شرایط خطرناک بودن | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض آلاینده‌ها بودن | نزدیکی فیزیکی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | فشار زمانی | پیامد خطا | قرار گرفتن در معرض شرایط خطرناک | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | نزدیکی فیزیکی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Biological Technicians | Calibration Technologists and Technicians | Cardiologists | Cardiovascular Technologists and Technicians | Chemical Technicians | Cytogenetic Technologists | Cytotechnologists | Endoscopy Technicians | Histology Technicians | Histotechnologists | Medical Equipment Preparers | Medical and Clinical Laboratory Technologists | Microbiologists | Neurodiagnostic Technologists | Nuclear Medicine Technologists | Phlebotomists | Physicians, Pathologists | Radiologic Technologists and Technicians | Surgical Assistants | Surgical Technologists</t>
+          <t>تکنسین‌های زیستی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | تکنسین‌های شیمی | تکنولوژیست‌های سیتوژنتیک | سیتوتکنولوژیست‌ها | تکنسین‌های آندوسکوپی | تکنیسین‌های هیستولوژی | هیستوتکنولوژیست‌ها | آماده‌سازان تجهیزات پزشکی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی هسته‌ای | فلبوتومیست‌ها | پزشکان، آسیب‌شناسان | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,12 +892,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Histology Technicians (تکنیسین‌های هیستولوژی)</t>
+          <t>تکنیسین‌های هیستولوژی (Histology Technicians)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Clinical Histology Technician (Clinical Histology Tech) | Histologic Technician (HT) | Histologist | Histology Consultant | Histology Coordinator | Histology Technician (HT) | Histotechnician</t>
+          <t>تکنسین بافت‌شناسی بالینی (Clinical Histology Tech) | تکنسین بافت‌شناسی (HT) | بافت‌شناس | مشاور بافت‌شناسی | هماهنگ‌کننده بافت‌شناسی | تکنسین بافت‌شناسی (HT) | تکنسین بافت‌شناسی</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | نظارت | سخنوری | علوم | نوشتن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | نظارت | سخن گفتن | علوم | نگارش</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | مهارت انگشتان | درک شفاهی | ثبات دست و بازو | استدلال قیاسی | نظم‌دهی اطلاعات | حساسیت به مسئله | درک نوشتاری | انعطاف‌پذیری دسته‌بندی | مهارت دستی | استدلال استقرایی | بیان نوشتاری | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دقت کنترل | توجه انتخابی</t>
+          <t>بینایی نزدیک | مهارت انگشتان | درک شفاهی | ثبات دست و بازو | استدلال قیاسی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک کتبی | انعطاف‌پذیری دسته‌بندی | مهارت دستی | استدلال استقرایی | بیان کتبی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دقت کنترل | توجه انتخابی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقت یا صحت | صرف زمان برای انجام حرکات تکراری | محیط داخلی و کنترل‌شده از نظر محیطی | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض آلاینده‌ها بودن | بحث‌های حضوری با افراد و درون تیم‌ها | در معرض شرایط خطرناک بودن | فشار زمانی | ایمیل | اهمیت تکرار وظایف یکسان | پیامد خطا | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | صرف زمان برای نشستن | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | در معرض تجهیزات خطرناک بودن | آزادی در تصمیم‌گیری | در معرض بیماری یا عفونت بودن</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض شرایط خطرناک | فشار زمانی | ایمیل | اهمیت تکرار وظایف یکسان | پیامد خطا | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | صرف زمان برای نشستن | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Biological Technicians | Cardiovascular Technologists and Technicians | Chemical Technicians | Cytogenetic Technologists | Cytotechnologists | Diagnostic Medical Sonographers | Endoscopy Technicians | Histotechnologists | Medical Equipment Preparers | Medical and Clinical Laboratory Technicians | Medical and Clinical Laboratory Technologists | Microbiologists | Molecular and Cellular Biologists | Neurodiagnostic Technologists | Nuclear Medicine Technologists | Phlebotomists | Physicians, Pathologists | Radiologic Technologists and Technicians | Surgical Assistants | Surgical Technologists</t>
+          <t>تکنسین‌های زیستی | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | تکنسین‌های شیمی | تکنولوژیست‌های سیتوژنتیک | سیتوتکنولوژیست‌ها | سونوگرافیست‌های پزشکی تشخیصی | تکنسین‌های آندوسکوپی | هیستوتکنولوژیست‌ها | آماده‌سازان تجهیزات پزشکی | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان مولکولی و سلولی | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی هسته‌ای | فلبوتومیست‌ها | پزشکان، آسیب‌شناسان | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cardiovascular Technologists and Technicians (تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی)</t>
+          <t>تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی (Cardiovascular Technologists and Technicians)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cardiac Cath Lab Technologist (Cardiac Catheterization Laboratory Technologist) | Cardiac Catheterization Technician | Cardiac Technician | Cardio Tech (Cardiovascular Technician) | Cardiology Technician | Cardiopulmonary Technician | Cardiovascular Technologist (CVT) | Electrocardiogram Technician (EKG Tech) | Registered Cardiovascular Invasive Specialist (RCIS)</t>
+          <t>تکنولوژیست آزمایشگاه آنژیوگرافی قلب | تکنسین آنژیوگرافی قلب | تکنسین قلب | تکنسین قلب و عروق (Cardio Tech) | تکنسین قلب | تکنسین قلبی‌ریوی | تکنولوژیست قلب و عروق (CVT) | تکنسین نوار قلب (EKG Tech) | کارشناس ثبت‌شده اقدامات تهاجمی قلب و عروق (RCIS)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخنوری | تفکر انتقادی | نظارت | درک مطلب | نوشتن | یادگیری فعال | علوم</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | درک مطلب | نگارش | یادگیری فعال | علوم</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | پزشکی و دندانپزشکی | زبان انگلیسی | کامپیوتر و الکترونیک | آموزش و پرورش</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | دید نزدیک | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | بیان نوشتاری | درک نوشتاری | سرعت ادراکی | انعطاف‌پذیری بستار | ثبات دست و بازو | دقت کنترل | مهارت انگشتان | مهارت دستی | توجه انتخابی | تقسیم زمان | سرعت بستار | انعطاف‌پذیری دسته‌بندی</t>
+          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان کتبی | درک کتبی | سرعت ادراکی | انعطاف‌پذیری بستار | ثبات دست و بازو | دقت کنترل | مهارت انگشتان | مهارت دستی | توجه انتخابی | تقسیم توجه | سرعت بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | نزدیکی فیزیکی | بحث‌های حضوری با افراد و درون تیم‌ها | اهمیت دقت یا صحت | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی و کنترل‌شده از نظر محیطی | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | تناوب تصمیم‌گیری | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | ایمیل | در معرض بیماری یا عفونت بودن | آزادی در تصمیم‌گیری | پیامد خطا | تعامل با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | در معرض تابش بودن | صرف زمان برای خم شدن یا چرخاندن بدن</t>
+          <t>ارتباط با دیگران | نزدیکی فیزیکی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | فراوانی تصمیم‌گیری | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | ایمیل | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | آزادی در تصمیم‌گیری | پیامد خطا | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض تابش | صرف زمان برای خم کردن یا چرخاندن بدن</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Anesthesiologist Assistants | Cardiologists | Diagnostic Medical Sonographers | Emergency Medical Technicians | Endoscopy Technicians | Magnetic Resonance Imaging Technologists | Medical and Clinical Laboratory Technicians | Medical and Clinical Laboratory Technologists | Neurodiagnostic Technologists | Nuclear Medicine Technologists | Ophthalmic Medical Technologists | Orthopedic Surgeons, Except Pediatric | Paramedics | Pediatric Surgeons | Radiation Therapists | Radiologic Technologists and Technicians | Radiologists | Respiratory Therapists | Surgical Assistants | Surgical Technologists</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان قلب | سونوگرافیست‌های پزشکی تشخیصی | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های آندوسکوپی | تکنولوژیست‌های تصویربرداری تشدید مغناطیسی | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی هسته‌ای | تکنولوژیست‌های پزشکی چشم‌پزشکی | جراحان ارتوپد، به‌جز کودکان | پارامدیک‌ها | جراحان کودکان | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | درمانگران تنفسی | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,42 +1006,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Diagnostic Medical Sonographers (سونوگرافیست‌های پزشکی تشخیصی)</t>
+          <t>سونوگرافیست‌های پزشکی تشخیصی (Diagnostic Medical Sonographers)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cardiac Sonographer | Diagnostic Medical Sonographer | Medical Sonographer | Registered Diagnostic Medical Sonographer (RDMS) | Sonographer | Staff Sonographer | Ultrasonographer | Ultrasound Technician (Ultrasound Tech) | Ultrasound Technologist (Ultrasound Tech)</t>
+          <t>سونوگرافیست قلب | سونوگرافیست تشخیص پزشکی | سونوگرافیست پزشکی | سونوگرافیست ثبت‌شده تشخیص پزشکی (RDMS) | سونوگرافیست | سونوگرافیست کادر درمان | متخصص اولتراسونوگرافی | تکنسین سونوگرافی (Ultrasound Tech) | تکنولوژیست سونوگرافی (Ultrasound Tech)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری روش‌های پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار پرونده پزشکی بیمار | نرم‌افزار EHR eClinicalWorks</t>
+          <t>نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار پرونده پزشکی بیمار | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | سخنوری | نظارت | تفکر انتقادی | یادگیری فعال | علوم | نوشتن | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نظارت | تفکر انتقادی | یادگیری فعال | علوم | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | زبان انگلیسی | فیزیک | پزشکی و دندانپزشکی | اداری | کامپیوتر و الکترونیک | روان‌شناسی | آموزش و پرورش</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فیزیک | پزشکی و دندان‌پزشکی | اداری | رایانه و الکترونیک | روان‌شناسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | حساسیت به مسئله | دید نزدیک | بیان نوشتاری | وضوح گفتار | تشخیص گفتار | استدلال استقرایی | دقت کنترل | ثبات دست و بازو | انعطاف‌پذیری بستار | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | سرعت بستار | هماهنگی چند اندامی | مهارت انگشتان | مهارت دستی | توجه انتخابی | تجسم | سرعت ادراکی | اصالت | روانی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | بیان کتبی | وضوح گفتار | تشخیص گفتار | استدلال استقرایی | دقت کنترل | ثبات دست و بازو | انعطاف‌پذیری بستار | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | سرعت بستار | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | توجه انتخابی | تجسم | سرعت ادراکی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>اهمیت دقت یا صحت | ارتباط با دیگران | نزدیکی فیزیکی | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | محیط داخلی و کنترل‌شده از نظر محیطی | اهمیت تکرار وظایف یکسان | مکالمات تلفنی | در معرض بیماری یا عفونت بودن | کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های حضوری با افراد و درون تیم‌ها | تناوب تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | تعامل با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای خم شدن یا چرخاندن بدن | پیامد خطا</t>
+          <t>اهمیت دقیق یا درست بودن | ارتباط با دیگران | نزدیکی فیزیکی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | مکالمات تلفنی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای خم کردن یا چرخاندن بدن | پیامد خطا</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Anesthesiologist Assistants | Anesthesiologists | Cardiologists | Cardiovascular Technologists and Technicians | Endoscopy Technicians | Magnetic Resonance Imaging Technologists | Medical and Clinical Laboratory Technicians | Medical and Clinical Laboratory Technologists | Neurodiagnostic Technologists | Nuclear Medicine Technologists | Ophthalmic Medical Technicians | Ophthalmic Medical Technologists | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Radiation Therapists | Radiologic Technologists and Technicians | Radiologists | Respiratory Therapists | Surgical Assistants | Surgical Technologists</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | تکنسین‌های آندوسکوپی | تکنولوژیست‌های تصویربرداری تشدید مغناطیسی | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی هسته‌ای | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | درمانگران تنفسی | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0048_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0048_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم پایه</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | درمان و مشاوره | خدمات مشتریان و خدمات فردی | زبان انگلیسی | شیمی | آموزش و تدریس | بازاریابی و فروش | امور اداری | مدیریت و امور اداری | جامعه‌شناسی و مردم‌شناسی | اقتصاد و حسابداری | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | زبان انگلیسی | شیمی | آموزش و پرورش | فروش و بازاریابی | اداری | مدیریت و اداره | جامعه‌شناسی و انسان‌شناسی | اقتصاد و حسابداری | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | دید نزدیک | بیان کتبی | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | انعطاف‌پذیری در نتیجه‌گیری | ابتکار و اصالت | توجه انتخابی | دید دور | سرعت ادراک</t>
+          <t>حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان کتبی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستار | اصالت | توجه انتخابی | بینایی دور | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>متخصصان طب سوزنی | پرستاران پیشرفته بالینی روان‌پزشکی | متخصصان آلرژی و ایمنی‌شناسی | متخصصان قلب و عروق | متخصصان کایروپراکتیک | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص داخلی | متخصصان مغز و اعصاب | پرستاران متخصص بالینی | متخصصان زنان و زایمان | چشم‌پزشکان، به جز اطفال | جراحان ارتوپدی، به جز اطفال | جراحان اطفال | پزشکان اطفال، عمومی | متخصصان طب فیزیکی و توان‌بخشی | دستیاران پزشک | روان‌پزشکان | متخصصان اورولوژی</t>
+          <t>متخصصان و کارشناسان طب سوزنی | پرستاران تخصصی روانپزشکی | متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیماری‌های قلب و عروق | کایروپراکتورها / متخصصان درمان دستی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | علوم پایه | نگارش | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | علوم | نگارش | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | روان‌شناسی | زیست‌شناسی</t>
+          <t>زبان انگلیسی | پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | آموزش و پرورش | روان‌شناسی | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | دید نزدیک | روانی ایده‌ها | سرعت ادراک | انعطاف‌پذیری در نتیجه‌گیری | مرتب‌سازی اطلاعات | ابتکار و اصالت | تشخیص رنگ‌ها | دید دور | چابکی انگشتان | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | روانی ایده‌ها | سرعت ادراکی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | اصالت | تشخیص رنگ بصری | بینایی دور | مهارت انگشتان | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | پرستاران بالینی فوق‌تخصصی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص داخلی | متخصصان مغز و اعصاب | پرستاران متخصص بالینی | متخصصان زنان و زایمان | فن‌آوران بینایی و چشم‌پزشکی | چشم‌پزشکان، به جز اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان اطفال | پزشکان اطفال، عمومی | متخصصان طب فیزیکی و توان‌بخشی | دستیاران پزشک | آسیب‌شناسان بالینی و تشریحی (پاتولوژیست‌ها) | روان‌پزشکان | متخصصان درمان تنفسی</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | پرستاران متخصص بالینی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | کارشناسان فناوری پزشکی چشم | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | پزشکان متخصص پاتولوژی | روان‌پزشکان | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | علوم پایه | شنیدن فعال | درک مطلب | نظارت | یادگیری فعال | نگارش | سخن گفتن | ریاضیات</t>
+          <t>تفکر انتقادی | علوم | گوش دادن فعال | درک مطلب | نظارت | یادگیری فعال | نگارش | سخن گفتن | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>شیمی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | زبان انگلیسی | زیست‌شناسی | ریاضیات | امور اداری | پزشکی و دندان‌پزشکی | آموزش و تدریس | مکانیک</t>
+          <t>شیمی | خدمات مشتری و شخصی | رایانه و الکترونیک | زبان انگلیسی | زیست‌شناسی | ریاضیات | اداری | پزشکی و دندان‌پزشکی | آموزش و پرورش | مکانیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دید نزدیک | استدلال استقرایی | درک کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات | درک شفاهی | استدلال قیاسی | انعطاف‌پذیری در طبقه‌بندی | بیان شفاهی | ثبات دست و بازو | دقت کنترل | چابکی انگشتان | انعطاف‌پذیری در نتیجه‌گیری | توجه انتخابی | تشخیص گفتار | تشخیص رنگ‌ها | بیان کتبی | چابکی دستی | سرعت ادراک | سرعت در نتیجه‌گیری | استدلال ریاضی | وضوح گفتار | دید دور | تجسم‌سازی | توانایی محاسبه</t>
+          <t>بینایی نزدیک | استدلال استقرایی | درک کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک شفاهی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | ثبات دست و بازو | دقت کنترل | مهارت انگشتان | انعطاف‌پذیری بستار | توجه انتخابی | تشخیص گفتار | تشخیص رنگ بصری | بیان کتبی | مهارت دستی | سرعت ادراکی | سرعت بستار | استدلال ریاضی | وضوح گفتار | بینایی دور | تجسم | توانایی عددی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنسین‌های زیست‌شناسی | متخصصان قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | تکنسین‌های شیمی | شیمی‌دان‌ها | کارشناسان سیتوژنتیک | سیتوتکنولوژیست‌ها | سونوگرافیست‌های تشخیصی | کاردان‌های پاتولوژی و بافت‌شناسی | کارشناسان پاتولوژی و بافت‌شناسی | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | میکروب‌شناسان | کارشناسان الکترودیاگنوستیک مغز و اعصاب | کارشناسان پزشکی هسته‌ای | خون‌گیرها (فلبوتومیست‌ها) | آسیب‌شناسان بالینی و تشریحی (پاتولوژیست‌ها) | کارشناسان و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | تکنسین‌های اتاق عمل</t>
+          <t>تکنسین‌های علوم زیستی | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | تکنسین‌های شیمی | شیمی‌دانان | کارشناسان سیتوژنتیک | سیتوتکنولوژیست‌ها / کارشناسان سیتولوژی | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | کاردان‌های پاتولوژی و بافت‌شناسی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | پژوهشگران و دانشمندان علوم پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | میکروبیولوژیست‌ها | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان و تکنسین‌های پزشکی هسته‌ای | کارشناسان و تکنسین‌های خون‌گیری | پزشکان متخصص پاتولوژی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان رادیولوژی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نگارش | سخن گفتن | شنیدن فعال | یادگیری فعال | علوم پایه | نظارت | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | نگارش | سخن گفتن | گوش دادن فعال | یادگیری فعال | علوم | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات | دید نزدیک | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | حساسیت به مسئله | انعطاف‌پذیری در طبقه‌بندی | انعطاف‌پذیری در نتیجه‌گیری | توجه انتخابی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ‌ها | سرعت ادراک | توانایی محاسبه | استدلال ریاضی | روانی ایده‌ها | چابکی انگشتان | ثبات دست و بازو</t>
+          <t>درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | سرعت ادراکی | توانایی عددی | استدلال ریاضی | روانی ایده‌ها | مهارت انگشتان | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان پزشکی | متخصصان بیوانفورماتیک | تکنسین‌های زیست‌شناسی | کارشناسان و تکنسین‌های قلب و عروق | سیتوتکنولوژیست‌ها | متخصصان ژنتیک | کاردان‌های پاتولوژی و بافت‌شناسی | کارشناسان پاتولوژی و بافت‌شناسی | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | میکروب‌شناسان | زیست‌شناسان سلولی و مولکولی | کارشناسان الکترودیاگنوستیک مغز و اعصاب | کارشناسان پزشکی هسته‌ای | خون‌گیرها (فلبوتومیست‌ها) | آسیب‌شناسان بالینی و تشریحی (پاتولوژیست‌ها) | کارشناسان و تکنسین‌های رادیولوژی | رادیولوژیست‌ها</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | تکنسین‌های علوم زیستی | کارشناسان و تکنسین‌های قلب و عروق | سیتوتکنولوژیست‌ها / کارشناسان سیتولوژی | متخصصان ژنتیک | کاردان‌های پاتولوژی و بافت‌شناسی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | پژوهشگران و دانشمندان علوم پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان و تکنسین‌های پزشکی هسته‌ای | کارشناسان و تکنسین‌های خون‌گیری | پزشکان متخصص پاتولوژی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان رادیولوژی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | پزشکی و دندان‌پزشکی | زبان انگلیسی | امور اداری</t>
+          <t>زیست‌شناسی | پزشکی و دندان‌پزشکی | زبان انگلیسی | اداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | دید نزدیک | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری در نتیجه‌گیری | ثبات دست و بازو | چابکی انگشتان | تشخیص رنگ‌ها | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | بیان شفاهی | توجه انتخابی | وضوح گفتار | تشخیص گفتار | دید دور | دقت کنترل | چابکی دستی | بیان کتبی</t>
+          <t>درک شفاهی | درک کتبی | بینایی نزدیک | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری بستار | ثبات دست و بازو | مهارت انگشتان | تشخیص رنگ بصری | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | توجه انتخابی | وضوح گفتار | تشخیص گفتار | بینایی دور | دقت کنترل | مهارت دستی | بیان کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های قلب و عروق | کارشناسان سیتوژنتیک | تکنسین‌های آندوسکوپی | کاردان‌های پاتولوژی و بافت‌شناسی | کارشناسان پاتولوژی و بافت‌شناسی | آماده‌سازان تجهیزات پزشکی | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | میکروب‌شناسان | کارشناسان الکترودیاگنوستیک مغز و اعصاب | کارشناسان پزشکی هسته‌ای | تکنسین‌های بینایی و چشم‌پزشکی | فن‌آوران بینایی و چشم‌پزشکی | خون‌گیرها (فلبوتومیست‌ها) | آسیب‌شناسان بالینی و تشریحی (پاتولوژیست‌ها) | کارشناسان و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
+          <t>کارشناسان و تکنسین‌های قلب و عروق | کارشناسان سیتوژنتیک | تکنسین‌های اندوسکوپی | کاردان‌های پاتولوژی و بافت‌شناسی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | پژوهشگران و دانشمندان علوم پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان و تکنسین‌های پزشکی هسته‌ای | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | کارشناسان و تکنسین‌های خون‌گیری | پزشکان متخصص پاتولوژی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان رادیولوژی | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال | یادگیری فعال | نگارش | علوم پایه</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | یادگیری فعال | نگارش | علوم</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | تولید و فرآوری | شیمی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری | آموزش و تدریس</t>
+          <t>زیست‌شناسی | تولید و فرآوری | شیمی | خدمات مشتری و شخصی | زبان انگلیسی | اداری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک کتبی | ثبات دست و بازو | درک شفاهی | حساسیت به مسئله | بیان کتبی | بیان شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات | توجه انتخابی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ‌ها | دید دور | چابکی انگشتان | انعطاف‌پذیری در طبقه‌بندی | استدلال استقرایی | دقت کنترل | انعطاف‌پذیری در نتیجه‌گیری</t>
+          <t>بینایی نزدیک | درک کتبی | ثبات دست و بازو | درک شفاهی | حساسیت به مسئله | بیان کتبی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | توجه انتخابی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | بینایی دور | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | دقت کنترل | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های زیست‌شناسی | کارشناسان و تکنسین‌های قلب و عروق | تکنسین‌های شیمی | کارشناسان سیتوژنتیک | سیتوتکنولوژیست‌ها | تکنسین‌های آندوسکوپی | کاردان‌های پاتولوژی و بافت‌شناسی | آماده‌سازان تجهیزات پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | میکروب‌شناسان | کارشناسان الکترودیاگنوستیک مغز و اعصاب | کارشناسان پزشکی هسته‌ای | فن‌آوران بینایی و چشم‌پزشکی | خون‌گیرها (فلبوتومیست‌ها) | آسیب‌شناسان بالینی و تشریحی (پاتولوژیست‌ها) | کارشناسان و تکنسین‌های رادیولوژی | دستیاران جراحی | تکنسین‌های اتاق عمل | کارشناسان و تکنسین‌های دامپزشکی</t>
+          <t>تکنسین‌های علوم زیستی | کارشناسان و تکنسین‌های قلب و عروق | تکنسین‌های شیمی | کارشناسان سیتوژنتیک | سیتوتکنولوژیست‌ها / کارشناسان سیتولوژی | تکنسین‌های اندوسکوپی | کاردان‌های پاتولوژی و بافت‌شناسی | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان و تکنسین‌های پزشکی هسته‌ای | کارشناسان فناوری پزشکی چشم | کارشناسان و تکنسین‌های خون‌گیری | پزشکان متخصص پاتولوژی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | دستیاران جراحی | تکنسین‌های اتاق عمل | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | علوم پایه | نظارت | نگارش | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | علوم | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>شیمی | زیست‌شناسی | زبان انگلیسی | ریاضیات | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | امور اداری | پزشکی و دندان‌پزشکی</t>
+          <t>شیمی | زیست‌شناسی | زبان انگلیسی | ریاضیات | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | اداری | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | بیان شفاهی | درک شفاهی | چابکی انگشتان | درک کتبی | استدلال قیاسی | بیان کتبی | چابکی دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری در نتیجه‌گیری | انعطاف‌پذیری در طبقه‌بندی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ‌ها | دقت کنترل | استدلال ریاضی | استدلال استقرایی | سرعت ادراک | توانایی محاسبه</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | مهارت انگشتان | درک کتبی | استدلال قیاسی | بیان کتبی | مهارت دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | دقت کنترل | استدلال ریاضی | استدلال استقرایی | سرعت ادراکی | توانایی عددی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های زیست‌شناسی | کارشناسان و تکنسین‌های کالیبراسیون | متخصصان قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | تکنسین‌های شیمی | کارشناسان سیتوژنتیک | سیتوتکنولوژیست‌ها | تکنسین‌های آندوسکوپی | کاردان‌های پاتولوژی و بافت‌شناسی | کارشناسان پاتولوژی و بافت‌شناسی | آماده‌سازان تجهیزات پزشکی | کارشناسان علوم آزمایشگاهی بالینی | میکروب‌شناسان | کارشناسان الکترودیاگنوستیک مغز و اعصاب | کارشناسان پزشکی هسته‌ای | خون‌گیرها (فلبوتومیست‌ها) | آسیب‌شناسان بالینی و تشریحی (پاتولوژیست‌ها) | کارشناسان و تکنسین‌های رادیولوژی | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
+          <t>تکنسین‌های علوم زیستی | تکنسین‌ها و کارشناسان فنی کالیبراسیون | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | تکنسین‌های شیمی | کارشناسان سیتوژنتیک | سیتوتکنولوژیست‌ها / کارشناسان سیتولوژی | تکنسین‌های اندوسکوپی | کاردان‌های پاتولوژی و بافت‌شناسی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان و تکنسین‌های پزشکی هسته‌ای | کارشناسان و تکنسین‌های خون‌گیری | پزشکان متخصص پاتولوژی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | نظارت | سخن گفتن | علوم پایه | نگارش</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | نظارت | سخن گفتن | علوم | نگارش</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>شیمی | زیست‌شناسی | زبان انگلیسی | امور اداری</t>
+          <t>شیمی | زیست‌شناسی | زبان انگلیسی | اداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی انگشتان | درک شفاهی | ثبات دست و بازو | استدلال قیاسی | مرتب‌سازی اطلاعات | حساسیت به مسئله | درک کتبی | انعطاف‌پذیری در طبقه‌بندی | چابکی دستی | استدلال استقرایی | بیان کتبی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دقت کنترل | توجه انتخابی</t>
+          <t>بینایی نزدیک | مهارت انگشتان | درک شفاهی | ثبات دست و بازو | استدلال قیاسی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک کتبی | انعطاف‌پذیری دسته‌بندی | مهارت دستی | استدلال استقرایی | بیان کتبی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دقت کنترل | توجه انتخابی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های زیست‌شناسی | کارشناسان و تکنسین‌های قلب و عروق | تکنسین‌های شیمی | کارشناسان سیتوژنتیک | سیتوتکنولوژیست‌ها | سونوگرافیست‌های تشخیصی | تکنسین‌های آندوسکوپی | کارشناسان پاتولوژی و بافت‌شناسی | آماده‌سازان تجهیزات پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | میکروب‌شناسان | زیست‌شناسان سلولی و مولکولی | کارشناسان الکترودیاگنوستیک مغز و اعصاب | کارشناسان پزشکی هسته‌ای | خون‌گیرها (فلبوتومیست‌ها) | آسیب‌شناسان بالینی و تشریحی (پاتولوژیست‌ها) | کارشناسان و تکنسین‌های رادیولوژی | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
+          <t>تکنسین‌های علوم زیستی | کارشناسان و تکنسین‌های قلب و عروق | تکنسین‌های شیمی | کارشناسان سیتوژنتیک | سیتوتکنولوژیست‌ها / کارشناسان سیتولوژی | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | تکنسین‌های اندوسکوپی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان و تکنسین‌های پزشکی هسته‌ای | کارشناسان و تکنسین‌های خون‌گیری | پزشکان متخصص پاتولوژی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت | درک مطلب | نگارش | یادگیری فعال | علوم پایه</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | درک مطلب | نگارش | یادگیری فعال | علوم</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | زبان انگلیسی | رایانه و الکترونیک | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | دید نزدیک | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | بیان کتبی | درک کتبی | سرعت ادراک | انعطاف‌پذیری در نتیجه‌گیری | ثبات دست و بازو | دقت کنترل | چابکی انگشتان | چابکی دستی | توجه انتخابی | تقسیم توجه | سرعت در نتیجه‌گیری | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان کتبی | درک کتبی | سرعت ادراکی | انعطاف‌پذیری بستار | ثبات دست و بازو | دقت کنترل | مهارت انگشتان | مهارت دستی | توجه انتخابی | تقسیم توجه | سرعت بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | متخصصان قلب و عروق | سونوگرافیست‌های تشخیصی | تکنسین‌های فوریت‌های پزشکی (EMT) | تکنسین‌های آندوسکوپی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | کارشناسان الکترودیاگنوستیک مغز و اعصاب | کارشناسان پزشکی هسته‌ای | فن‌آوران بینایی و چشم‌پزشکی | جراحان ارتوپدی، به جز اطفال | کارشناسان فوریت‌های پزشکی (پارامدیک) | جراحان اطفال | پرتو‌درمانگران (تکنولوژیست‌های رادیوتراپی) | کارشناسان و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | متخصصان درمان تنفسی | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیماری‌های قلب و عروق | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های اندوسکوپی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان و تکنسین‌های پزشکی هسته‌ای | کارشناسان فناوری پزشکی چشم | جراحان ارتوپدی، غیر از اطفال | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان رادیولوژی | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | نظارت | تفکر انتقادی | یادگیری فعال | علوم پایه | نگارش | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نظارت | تفکر انتقادی | یادگیری فعال | علوم | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | فیزیک | پزشکی و دندان‌پزشکی | امور اداری | رایانه و الکترونیک | روان‌شناسی | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فیزیک | پزشکی و دندان‌پزشکی | اداری | رایانه و الکترونیک | روان‌شناسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | دید نزدیک | بیان کتبی | وضوح گفتار | تشخیص گفتار | استدلال استقرایی | دقت کنترل | ثبات دست و بازو | انعطاف‌پذیری در نتیجه‌گیری | استدلال قیاسی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | سرعت در نتیجه‌گیری | هماهنگی چند عضو بدن | چابکی انگشتان | چابکی دستی | توجه انتخابی | تجسم‌سازی | سرعت ادراک | ابتکار و اصالت | روانی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | بیان کتبی | وضوح گفتار | تشخیص گفتار | استدلال استقرایی | دقت کنترل | ثبات دست و بازو | انعطاف‌پذیری بستار | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | سرعت بستار | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | توجه انتخابی | تجسم | سرعت ادراکی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | تکنسین‌های آندوسکوپی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | کارشناسان الکترودیاگنوستیک مغز و اعصاب | کارشناسان پزشکی هسته‌ای | تکنسین‌های بینایی و چشم‌پزشکی | فن‌آوران بینایی و چشم‌پزشکی | جراحان ارتوپدی، به جز اطفال | جراحان اطفال | پرتو‌درمانگران (تکنولوژیست‌های رادیوتراپی) | کارشناسان و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | متخصصان درمان تنفسی | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | تکنسین‌های اندوسکوپی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان و تکنسین‌های پزشکی هسته‌ای | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان رادیولوژی | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
